--- a/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
+++ b/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
@@ -106,7 +106,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -128,11 +128,44 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -168,6 +201,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -533,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -781,6 +815,237 @@
       <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Cảm ơn anh Việt rất nhiều, nhờ anh mà em tự tin bấm máy quay ngay ngày hôm sau!</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-0004</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 07:01:36</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Offline Thực Chiến K12 - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Trang</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý pháp chế MEDLATEC (Chuẩn bị mở cty luật riêng)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://facebook.com/thutrang.law</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>TikTok Video</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định đăng ký chỉ sau 20 giây xem video anh Việt nói về băm nhỏ phân cảnh và ứng dụng AI đa ngành</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Tư duy rất mới về ứng dụng AI, kỹ năng quay dựng và cách làm marketing đa ngành. Tự tin và định hướng rõ ràng hơn rất nhiều.</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>- Cần kiểm soát danh sách check-in vào lớp chặt chẽ hơn
+- Gửi link khảo sát ngắn trước buổi học
+- Thăm hỏi học viên vắng mặt hoặc về sớm
+- Dành 10p cuối giới thiệu gói nâng cao kèm ưu đãi tại lớp
+- Tư vấn rõ ưu đãi giảm 10% khi đăng ký nhóm 2 người</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>AI Chuyên Sâu Tự Động Hóa Video, Xây Kênh Thương Hiệu Cá Nhân</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Zalo</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị Thầy mang lại là điều vô giá đối với Em ạ! Chúc Thầy và đội ngũ luôn giữ ngọn lửa nhiệt huyết.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-0005</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 07:01:36</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Offline Thực Chiến K12 - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Trần Quốc Huy</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Chủ chuỗi thời trang nam tại Hải Phòng</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://tiktok.com/@huytran.menswear</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Facebook Reels / Post</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Video bóc tách kịch bản 3 tầng bán quần áo không bị flop</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Nắm vững kỹ thuật setup 2 máy quay và cách nói chuyện tự nhiên trước ống kính</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>- Mong muốn có thêm buổi thực hành bối cảnh ngoại cảnh
+- Khâu tài liệu phát tay nên in sớm hơn</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Video Ads Bán Hàng Chuyển Đổi Cao</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Zalo</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Cảm ơn anh Việt nhiều, về Hải Phòng em sẽ bắt tay bấm máy quay ngay loạt video đầu tiên!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-0006</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 07:01:36</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Online Video Masterclass K05</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Lê Hoàng Minh</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0905123456</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Môi giới Bất động sản cao cấp TP.HCM</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@hoangminh.batdongsan</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>YouTube Video / Shorts</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Video hướng dẫn làm video BĐS không cần máy xịn, chỉ cần điện thoại và đèn</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Biết cách làm kịch bản đánh trúng nỗi đau người mua nhà và quy trình dựng video nhanh trong 15 phút</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>- Buổi Zoom nên tăng thêm thời lượng hỏi đáp 1-1
+- Gói nâng cao nên có nhóm hỗ trợ sửa video hàng tuần</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>AI Chuyên Sâu Tự Động Hóa Video, Kèm 1-1 Setup Studio &amp; Thực Chiến</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Mong anh sớm mở workshop trực tiếp tại Sài Gòn để anh em trong Nam được gặp anh!</t>
         </is>
       </c>
     </row>
@@ -820,36 +1085,36 @@
           <t>Tổng Số Phản Hồi</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="B3" s="13" t="n"/>
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Điểm Hài Lòng Trung Bình (NPS)</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n"/>
+      <c r="D3" s="13" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Tỷ Lệ Quan Tâm Nâng Cao</t>
         </is>
       </c>
-      <c r="F3" s="7" t="n"/>
+      <c r="F3" s="13" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8">
         <f>COUNTA('Dữ Liệu Khảo Sát'!A2:A1000)</f>
         <v/>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="13" t="n"/>
       <c r="C4" s="9">
         <f>AVERAGE('Dữ Liệu Khảo Sát'!L2:L1000)</f>
         <v/>
       </c>
-      <c r="D4" s="7" t="n"/>
+      <c r="D4" s="13" t="n"/>
       <c r="E4" s="10">
         <f>COUNTIF('Dữ Liệu Khảo Sát'!M2:M1000, "*AI*")/COUNTA('Dữ Liệu Khảo Sát'!A2:A1000)</f>
         <v/>
       </c>
-      <c r="F4" s="7" t="n"/>
+      <c r="F4" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -871,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -990,6 +1255,111 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Trang</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý pháp chế MEDLATEC (Chuẩn bị mở cty luật riêng)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://facebook.com/thutrang.law</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Gói quà Prompt AI + AI Chuyên Sâu Tự Động Hóa Video, Xây Kênh Thương Hiệu Cá Nhân</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Đã tự động gắn tag &amp; sẵn sàng gửi quà Zalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Trần Quốc Huy</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Chủ chuỗi thời trang nam tại Hải Phòng</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://tiktok.com/@huytran.menswear</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Gói quà Prompt AI + Video Ads Bán Hàng Chuyển Đổi Cao</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Đã tự động gắn tag &amp; sẵn sàng gửi quà Zalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Lê Hoàng Minh</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Môi giới Bất động sản cao cấp TP.HCM</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@hoangminh.batdongsan</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>0905123456</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Gói quà Prompt AI + AI Chuyên Sâu Tự Động Hóa Video, Kèm 1-1 Setup Studio &amp; Thực Chiến</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Đã tự động gắn tag &amp; sẵn sàng gửi quà Zalo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
+++ b/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -694,6 +694,66 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 18:04:24</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Lớp Offline Thực Chiến - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Trần Tuấn Anh (Test Kiểm Thử 100%)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0912888999</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Giám đốc công ty du lịch. Muốn quay video review tour trải nghiệm và chia sẻ mẹo du lịch.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://tiktok.com/@tuananh_travel
+https://facebook.com/tuananhtravel</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Xem video băm kịch bản 3 tầng, thấy thực tế quá nên nhắn tin và đăng ký.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2 ngày học cực kỳ đáng giá, vỡ ra cách tư duy kịch bản và cách cầm máy tự tin.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>2 ảnh</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>📁 Link Drive: https://docs.google.com/spreadsheets/d/15zgMk-Xow8E_Ha1qgWbGtgWEYwygXyAMqFxkczghokM/edit
+1. anh_lop_hoc_1.jpg (195 KB)
+2. anh_lop_hoc_2.jpg (210 KB)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -705,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -826,6 +886,42 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Trần Tuấn Anh</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0912888999</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Du lịch &amp; Tour trải nghiệm</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>tiktok.com/@tuananh_travel
+facebook.com/tuananhtravel</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2 ảnh</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>✅ Đã lưu Zalo, đã bấm follow kênh</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
+++ b/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,124 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 18:21:02</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Lớp Offline Thực Chiến - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Phạm Hoàng Long (Test Persistent 100%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0933555777</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Kinh doanh thiết bị điện tử thông minh. Muốn quay video so sánh tính năng và unbox sản phẩm.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://tiktok.com/@hoanglong.tech
+https://youtube.com/@hoanglongreview</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Xem video bóc 3 tầng trên Reels, thấy quá chân thực.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Lớp học thực chiến chất lượng, thực hành cầm máy quay rất trực quan.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>1 ảnh</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>📁 Link Drive: https://docs.google.com/spreadsheets/d/1J9ZrjLxTba9R-wuet1n_J_hKcL0PVtQDD_ag65Ewx04/edit
+1. anh_thuc_hanh_quay.jpg (80 KB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 18:22:09</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Lớp Offline Thực Chiến - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Nguyễn Hoàng Nam (Test Trình Duyệt Thật)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0966888999</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Chủ chuỗi nha khoa thẩm mỹ tại Hà Nội. Muốn xây kênh chia sẻ kiến thức nha khoa không đau và bọc sứ thẩm mỹ. Đang bí phần hook 3s đầu.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://tiktok.com/@nam.nhakhoa
+https://facebook.com/namdental.clinic</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Lướt thấy video anh chia sẻ bóc kịch bản 3 tầng trên TikTok. Xem cuốn quá nên xem tiếp 4 video rồi nhắn tin đăng ký chuyển khoản luôn.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2 ngày học rất đã, vỡ ra cách setup 2 góc máy và tư duy băm cảnh. Hôm nào rảnh em mời anh ly cafe nhé!</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>1 ảnh</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>📁 Link Drive: https://docs.google.com/spreadsheets/d/1J9ZrjLxTba9R-wuet1n_J_hKcL0PVtQDD_ag65Ewx04/edit
+1. anh_chup_lop_hoc_test.jpg (82 KB)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -765,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -922,6 +1040,78 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Phạm Hoàng Long</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0933555777</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Điện tử thông minh &amp; Unbox</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>tiktok.com/@hoanglong.tech
+youtube.com/@hoanglongreview</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1 ảnh</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>✅ Đã lưu Zalo, đã bấm follow kênh</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Hoàng Nam</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0966888999</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Nha khoa thẩm mỹ &amp; Răng sứ</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>tiktok.com/@nam.nhakhoa
+facebook.com/namdental.clinic</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1 ảnh</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>✅ Đã lưu Zalo, đã bấm follow kênh</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
+++ b/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dữ Liệu Khảo Sát &amp; Ảnh" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Danh Bạ &amp; Kênh" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dữ Liệu Khảo Sát" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard Tổng Quan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Kết Nối &amp; Tặng Quà" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +31,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -39,28 +40,47 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="10"/>
+      <color rgb="00059669"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00F8FAFC"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00059669"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="002563EB"/>
-      <sz val="9"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00059669"/>
-      <sz val="9"/>
+      <color rgb="00D97706"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,8 +95,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFDF5"/>
-        <bgColor rgb="00ECFDF5"/>
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00334155"/>
+        <bgColor rgb="00334155"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,9 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,19 +144,29 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,20 +533,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -536,339 +576,286 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Số Zalo Hay Dùng</t>
+          <t>Số Điện Thoại / Zalo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Mảng Kinh Doanh &amp; Định Hướng AI</t>
+          <t>Nghề Nghiệp / Dự Án</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Danh Sách Link Kênh / Video / FB</t>
+          <t>Link Kênh / Profile</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Hành Trình Biết Đến &amp; Xem Video</t>
+          <t>Nguồn Biết Đến</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Góp Ý Thẳng Thắn &amp; Lời Nhắn</t>
+          <t>Video Ấn Tượng Nhất</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Số Lượng Ảnh</t>
+          <t>Điều Tâm Đắc Nhất</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Link Drive &amp; Tên File Ảnh Kỷ Niệm</t>
+          <t>Góp Ý Vận Hành &amp; Lớp Học</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Điểm Đánh Giá (1-10)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Nhu Cầu Khóa Nâng Cao</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Kênh Liên Hệ Ưu Tiên</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Lời Nhắn Nhủ Riêng</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="95" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KS-2026-0001</t>
+          <t>KS-2026-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 08:15:20</t>
+          <t>24/08/2026 23:16:30</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Lớp Offline Thực Chiến - Hà Nội</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+          <t>30 Ngày Học Làm Nội Dung Viral / Offline Thực Chiến</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Học viên ngành Phân Bón Nông Nghiệp</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>0988***888</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Kinh doanh &amp; Sản xuất Phân bón Nông nghiệp (Có nhiều cảnh đẹp &amp; tư liệu thực tế nhưng chỉ biết giơ máy lên quay, chưa biết dựng)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://facebook.com/30ngayviral.fedu.vn</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Lướt Facebook Reels va vào video của anh Việt</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Xem liền 5 video chia sẻ cách bóc kịch bản mộc mạc và định hướng làm nội dung</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Nội dung mộc mạc, thực chiến đánh trúng vấn đề. Không cần 7 tiếng hay 11 điểm chạm để chốt đơn, xem đúng 5 clip là điền form chốt đi học ngay!</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Tư vấn và gọi điện cực kỳ nhanh gọn, đăng ký xong là chốt đơn đi học luôn không cần tư vấn lòng vòng.</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AI Băm kịch bản, Xây dựng kênh thực chiến ngành nông nghiệp &amp; phân bón</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Zalo</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Em thề là trước đây em không hề biết anh là ai luôn ấy :))) cũng không mất 7 tiếng để chốt đơn đâu, xem đúng 5 clip là chốt, lúc chốt còn chưa kịp theo dõi page thầy haha!</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 09:30:15</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Offline Thực Chiến K12 - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Nguyễn Thu Trang</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>0912345678</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Luật sư pháp chế (Chuẩn bị mở văn phòng luật riêng). Muốn làm dạng video case 45s như kênh tiktok.com/@luatsucuocsong. Cần AI bóc tách kịch bản và setup 2 góc máy.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>https://facebook.com/thutrang.law
-https://tiktok.com/@thutrang_legal</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Lướt thấy video anh Việt chia sẻ về băm phân cảnh 3 tầng và góc nhìn AI thực chiến. Xem đúng 20 giây là thấy cách nói quá mộc mạc, không đao to búa lớn nên nhắn tin đăng ký và chuyển khoản luôn.</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>• Khâu tư vấn: Các bạn nên tư vấn rõ ưu đãi giảm 10% khi đăng ký nhóm từ đầu để học viên rủ thêm bạn.
-• Lớp học: Nhịp dạy rất thực chiến, tâm đắc nhất là tự tin cầm máy và tư duy băm nhỏ phân cảnh.
-• Lời nhắn: Cảm ơn anh nhiều, hôm nào rảnh em mời anh ly cafe nhé!</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>2 ảnh</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>📁 Link Drive: https://drive.google.com/drive/folders/1aBcDeFgHiJkLmNoPqRsTuVwXyZ_NguyenThuTrang
-1. lop_hoc_thuc_hanh_quay_2_may.jpg (185 KB)
-2. anh_chup_chung_anh_viet.jpg (210 KB)</t>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý pháp chế MEDLATEC (Chuẩn bị mở cty luật)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://facebook.com/thutrang.law</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Video TikTok / Reel (Quyết định sau 20s xem video)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Video anh Việt nói về băm nhỏ phân cảnh và tư duy làm video AI đa ngành</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Tư duy rất mới về ứng dụng AI, kỹ năng quay dựng và cách làm marketing đa ngành, định hướng rõ ràng</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>- Cần kiểm soát danh sách check-in chặt chẽ hơn
+- Gửi link khảo sát ngắn trước buổi học
+- Thăm hỏi học viên vắng/về sớm
+- Giới thiệu gói nâng cao 10p cuối kèm ưu đãi tại lớp
+- Tư vấn rõ ưu đãi giảm 10% khi đăng ký nhóm 2 người</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>AI Chuyên Sâu, Xây dựng thương hiệu cá nhân Luật Sư</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Zalo</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị Thầy mang lại là điều vô giá đối với Em ạ! Chúc Thầy luôn giữ ngọn lửa nhiệt huyết.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="95" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>KS-2026-0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 08:20:45</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Lớp Offline Thực Chiến - Hà Nội</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KS-2026-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 10:15:40</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Offline Thực Chiến K12 - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Trần Quốc Huy</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0987654321</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Chủ thương hiệu thời trang nam tại Hải Phòng. Muốn làm kênh chia sẻ cách phối đồ và video ads chuyển đổi cao.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>https://tiktok.com/@huytran.menswear
-https://youtube.com/@huytranstyle</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Thấy video Facebook Reels anh Việt bóc tách kịch bản 3 tầng bán quần áo. Thấy chuẩn bài quá nên tìm kênh xem thêm 3 video nữa rồi bấm đăng ký luôn.</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>• 2 ngày học rất đã, vỡ ra cách setup ánh sáng và cách bóc tách video đối thủ.
-• Góp ý: Khâu check-in buổi sáng nên gửi link khảo sát trước để anh nắm nhu cầu từng người sớm hơn.
-• Nhắn nhủ: Về Hải Phòng em bấm máy quay ngay loạt video đầu tiên gửi anh xem nhé!</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>2 ảnh</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>📁 Link Drive: https://drive.google.com/drive/folders/1xYzAbCdEfGhIjKlMnOpQrStUvWx_TranQuocHuy
-1. khong_khi_thuc_hanh_setup_den.jpg (192 KB)
-2. chup_ky_niem_ca_lop_ha_noi.jpg (245 KB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>KS-2026-0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 18:04:24</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Lớp Offline Thực Chiến - Hà Nội</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Trần Tuấn Anh (Test Kiểm Thử 100%)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0912888999</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Giám đốc công ty du lịch. Muốn quay video review tour trải nghiệm và chia sẻ mẹo du lịch.</t>
+          <t>Chủ thương hiệu thời trang nam tại Hải Phòng</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>https://tiktok.com/@tuananh_travel
-https://facebook.com/tuananhtravel</t>
+          <t>https://tiktok.com/@huytran.menswear</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Xem video băm kịch bản 3 tầng, thấy thực tế quá nên nhắn tin và đăng ký.</t>
+          <t>YouTube Shorts / Facebook Reels</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2 ngày học cực kỳ đáng giá, vỡ ra cách tư duy kịch bản và cách cầm máy tự tin.</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>2 ảnh</t>
+          <t>Video phân tích kịch bản video bán hàng thời trang 3 tầng</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Biết cách setup 2 máy quay và ánh sáng chuyên nghiệp, không còn sợ đứng trước ống kính</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>📁 Link Drive: https://docs.google.com/spreadsheets/d/15zgMk-Xow8E_Ha1qgWbGtgWEYwygXyAMqFxkczghokM/edit
-1. anh_lop_hoc_1.jpg (195 KB)
-2. anh_lop_hoc_2.jpg (210 KB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>KS-2026-0004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 18:21:02</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Lớp Offline Thực Chiến - Hà Nội</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Phạm Hoàng Long (Test Persistent 100%)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0933555777</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Kinh doanh thiết bị điện tử thông minh. Muốn quay video so sánh tính năng và unbox sản phẩm.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>https://tiktok.com/@hoanglong.tech
-https://youtube.com/@hoanglongreview</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Xem video bóc 3 tầng trên Reels, thấy quá chân thực.</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Lớp học thực chiến chất lượng, thực hành cầm máy quay rất trực quan.</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>1 ảnh</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>📁 Link Drive: https://docs.google.com/spreadsheets/d/1J9ZrjLxTba9R-wuet1n_J_hKcL0PVtQDD_ag65Ewx04/edit
-1. anh_thuc_hanh_quay.jpg (80 KB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>KS-2026-0005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 18:22:09</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Lớp Offline Thực Chiến - Hà Nội</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Nguyễn Hoàng Nam (Test Trình Duyệt Thật)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0966888999</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Chủ chuỗi nha khoa thẩm mỹ tại Hà Nội. Muốn xây kênh chia sẻ kiến thức nha khoa không đau và bọc sứ thẩm mỹ. Đang bí phần hook 3s đầu.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>https://tiktok.com/@nam.nhakhoa
-https://facebook.com/namdental.clinic</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Lướt thấy video anh chia sẻ bóc kịch bản 3 tầng trên TikTok. Xem cuốn quá nên xem tiếp 4 video rồi nhắn tin đăng ký chuyển khoản luôn.</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>2 ngày học rất đã, vỡ ra cách setup 2 góc máy và tư duy băm cảnh. Hôm nào rảnh em mời anh ly cafe nhé!</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>1 ảnh</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>📁 Link Drive: https://docs.google.com/spreadsheets/d/1J9ZrjLxTba9R-wuet1n_J_hKcL0PVtQDD_ag65Ewx04/edit
-1. anh_chup_lop_hoc_test.jpg (82 KB)</t>
+          <t>Khóa học rất thực chiến, mong có thêm buổi thực hành ngoài trời</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Video Ads Chuyển Đổi Cao, Automation Video</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Zalo</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Cảm ơn anh Việt rất nhiều, nhờ anh mà em tự tin bấm máy quay ngay ngày hôm sau!</t>
         </is>
       </c>
     </row>
@@ -883,232 +870,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>📊 BÁO CÁO TỔNG HỢP KHẢO SÁT &amp; INSIGHT HỌC VIÊN - VIETMAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Tổng Số Phản Hồi</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Điểm Hài Lòng Trung Bình (NPS)</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Tỷ Lệ Quan Tâm Nâng Cao</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8">
+        <f>COUNTA('Dữ Liệu Khảo Sát'!A2:A1000)</f>
+        <v/>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="9">
+        <f>AVERAGE('Dữ Liệu Khảo Sát'!L2:L1000)</f>
+        <v/>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="10">
+        <f>COUNTIF('Dữ Liệu Khảo Sát'!M2:M1000, "*AI*")/COUNTA('Dữ Liệu Khảo Sát'!A2:A1000)</f>
+        <v/>
+      </c>
+      <c r="F4" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Họ Và Tên</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Số Zalo</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Mảng Kinh Doanh</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Link Kênh / Video Đã Gửi</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Số Lượng Ảnh</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Trạng Thái Theo Dõi</t>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Họ Tên Học Viên</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Nghề Nghiệp / Dự Án</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Link Kênh / Profile</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Zalo / SĐT</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Nhu Cầu Độc Quyền</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Đã Kết Nối / Tặng Quà</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>Học viên ngành Phân Bón Nông Nghiệp</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Kinh doanh &amp; Sản xuất Phân bón Nông nghiệp</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>https://facebook.com/30ngayviral.fedu.vn</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>0988***888</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Gói prompt AI băm cảnh nông nghiệp + tư duy hook 3s</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Đã kết nối Zalo &amp; tư vấn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>Nguyễn Thu Trang</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý pháp chế MEDLATEC (Mở cty luật)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://facebook.com/thutrang.law</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>0912345678</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Luật sư pháp chế (Mở văn phòng)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>https://facebook.com/thutrang.law
-https://tiktok.com/@thutrang_legal</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2 ảnh</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Đã lưu Zalo, đã bấm follow kênh</t>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Gói prompt AI kịch bản luật sư + template branding</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Đã add Zalo &amp; gửi quà</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Trần Quốc Huy</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Chủ thương hiệu thời trang nam tại Hải Phòng</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://tiktok.com/@huytran.menswear</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>0987654321</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Thời trang nam Hải Phòng</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>https://tiktok.com/@huytran.menswear
-https://youtube.com/@huytranstyle</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2 ảnh</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Đã lưu Zalo, đang chờ video đầu tay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Trần Tuấn Anh</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0912888999</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Du lịch &amp; Tour trải nghiệm</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>tiktok.com/@tuananh_travel
-facebook.com/tuananhtravel</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2 ảnh</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>✅ Đã lưu Zalo, đã bấm follow kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Phạm Hoàng Long</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0933555777</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Điện tử thông minh &amp; Unbox</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>tiktok.com/@hoanglong.tech
-youtube.com/@hoanglongreview</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1 ảnh</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>✅ Đã lưu Zalo, đã bấm follow kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Hoàng Nam</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0966888999</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Nha khoa thẩm mỹ &amp; Răng sứ</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>tiktok.com/@nam.nhakhoa
-facebook.com/namdental.clinic</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1 ảnh</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>✅ Đã lưu Zalo, đã bấm follow kênh</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Checklist setup 2 máy quay + sound effect bán hàng</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Đã follow kênh TikTok</t>
         </is>
       </c>
     </row>
